--- a/Session 8 - Treap For Time Series Data/DS Lab.xlsx
+++ b/Session 8 - Treap For Time Series Data/DS Lab.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\varin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\varin\Documents\Data Structure Git\Data-Structure-Library-1402\Session 8 - Treap For Time Series Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD8609F5-A2BB-4481-AF83-C52811F91255}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{478F8050-8F48-4E15-AE32-180E27220FF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="21">
   <si>
     <t xml:space="preserve">Student Name </t>
   </si>
@@ -83,12 +83,6 @@
   </si>
   <si>
     <t>Name</t>
-  </si>
-  <si>
-    <t>محمدرضا امینی</t>
-  </si>
-  <si>
-    <t>سید محمد مهدی رضوی</t>
   </si>
 </sst>
 </file>
@@ -249,41 +243,41 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -521,38 +515,30 @@
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
     </row>
-    <row r="2" spans="1:7" s="12" customFormat="1" ht="39.6">
-      <c r="A2" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" s="14">
-        <v>402222020</v>
-      </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-    </row>
-    <row r="3" spans="1:7" s="12" customFormat="1" ht="39.6">
-      <c r="A3" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="14">
-        <v>402222073</v>
-      </c>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
+    <row r="2" spans="1:7" s="9" customFormat="1" ht="39.6">
+      <c r="A2" s="12"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+    </row>
+    <row r="3" spans="1:7" s="9" customFormat="1" ht="39.6">
+      <c r="A3" s="13"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
       <c r="F4" s="3"/>
     </row>
     <row r="5" spans="1:7" ht="13.2">
@@ -574,19 +560,19 @@
       <c r="F5" s="3"/>
     </row>
     <row r="6" spans="1:7" ht="22.5" customHeight="1">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="5">
         <v>8</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="5">
         <v>4.5999999999999996</v>
       </c>
       <c r="F6" s="3"/>
@@ -612,10 +598,10 @@
       <c r="F8" s="3"/>
     </row>
     <row r="9" spans="1:7" ht="22.5" customHeight="1">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="5" t="s">
         <v>20</v>
       </c>
       <c r="C9" s="3"/>
@@ -624,140 +610,140 @@
       <c r="F9" s="3"/>
     </row>
     <row r="10" spans="1:7" ht="26.25" customHeight="1">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="5" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="26.25" customHeight="1">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9" t="s">
+      <c r="C11" s="17"/>
+      <c r="D11" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9" t="s">
+      <c r="E11" s="17"/>
+      <c r="F11" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="9"/>
+      <c r="G11" s="17"/>
     </row>
     <row r="12" spans="1:7" ht="22.5" customHeight="1">
-      <c r="A12" s="9"/>
-      <c r="B12" s="10" t="s">
+      <c r="A12" s="17"/>
+      <c r="B12" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="G12" s="7" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="22.5" customHeight="1">
-      <c r="A13" s="8">
+      <c r="A13" s="6">
         <v>100000</v>
       </c>
-      <c r="B13" s="8">
+      <c r="B13" s="6">
         <v>0.336701869964599</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="6">
         <v>0.53483009338378895</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="6">
         <v>11.2649910449981</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E13" s="6">
         <v>0.78035998344421298</v>
       </c>
-      <c r="F13" s="8">
+      <c r="F13" s="6">
         <v>3.3026456832885701E-2</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G13" s="6">
         <v>3.3149957656860303E-2</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="22.5" customHeight="1">
-      <c r="A14" s="8">
+      <c r="A14" s="6">
         <v>400000</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B14" s="6">
         <v>1.9987928867339999</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="6">
         <v>4.04156422615051</v>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="8">
         <v>427.13161087036099</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="6">
         <v>3.4698641300201398</v>
       </c>
-      <c r="F14" s="8">
+      <c r="F14" s="6">
         <v>0.17165422439575101</v>
       </c>
-      <c r="G14" s="8">
+      <c r="G14" s="6">
         <v>0.20529699325561501</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="22.5" customHeight="1">
-      <c r="A15" s="8">
+      <c r="A15" s="6">
         <v>600000</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="6">
         <v>3.2469966411590501</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="6">
         <v>7.0603601932525599</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="6">
         <v>5.4502000808715803</v>
       </c>
-      <c r="F15" s="8">
+      <c r="F15" s="6">
         <v>0.289706230163574</v>
       </c>
-      <c r="G15" s="8">
+      <c r="G15" s="6">
         <v>0.29903149604797302</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="22.5" customHeight="1">
-      <c r="A16" s="8">
+      <c r="A16" s="6">
         <v>1000000</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="6">
         <v>6.1797692775726301</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="6">
         <v>11.768546104431101</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E16" s="8">
+      <c r="E16" s="6">
         <v>10.2140684127807</v>
       </c>
-      <c r="F16" s="8">
+      <c r="F16" s="6">
         <v>0.64054632186889604</v>
       </c>
-      <c r="G16" s="8">
+      <c r="G16" s="6">
         <v>0.87069463729858398</v>
       </c>
     </row>
